--- a/stories/arbres/ATOM-SAN.HYG.002-05.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, le soleil entre dans la salle de bain. Bénédicte sent l'eau tiède. Papa l'appelle. Papa tend la brosse jaune. Bénédicte prend la brosse. Un adulte est avec elle. C'est papa. Ils se brossent ensemble. La brosse va en haut. La brosse va en bas. Bénédicte sent la mousse. Ça goûte un peu la menthe. Parce qu'elle brosse le matin, ses dents sont propres. Elle rince sa bouche. Elle range la brosse. Plus tard, le soir arrive. La lumière est douce. Papa dit : c'est l'heure. Bénédicte revient. Elle prend encore la brosse. Papa, l'adulte, se brosse aussi. Matin et soir, c'est pareil. La brosse chatouille un peu. Papa dit : matin et soir, avec un adulte. Bénédicte répète : matin, soir, brosse. Elle pose la brosse dans le gobelet.</t>
+          <t>Le matin, le soleil entre dans la salle de bain. Bénédicte sent l'eau tiède. Papa l'appelle. Papa tend la brosse jaune. Bénédicte prend la brosse. Un adulte est avec elle. C'est papa. Ils se brossent ensemble. La brosse va en haut. La brosse va en bas. Bénédicte sent la mousse. Ça goûte un peu la menthe. Parce qu'elle brosse le matin, ses dents sont propres. Elle rince sa bouche. Elle range la brosse. Plus tard, le soir arrive. La lumière est douce. C'est l'heure. Bénédicte revient. Elle prend encore la brosse. Papa, l'adulte, se brosse aussi. Matin et soir, c'est pareil. La brosse chatouille un peu. Matin et soir, avec un adulte. Bénédicte répète : matin, soir, brosse. Elle pose la brosse dans le gobelet.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, le soleil entre dans la salle de bain. Bénédicte sent l'eau tiède. Papa l'appelle. Papa tend la brosse jaune. Bénédicte prend la brosse. Un adulte est avec elle. C'est papa. Ils se brossent ensemble. La brosse va en haut. La brosse va en bas. Bénédicte sent la mousse. Ça goûte un peu la menthe. Parce qu'elle brosse le matin, ses dents sont propres. Elle rince sa bouche. Elle range la brosse. Plus tard, le soir arrive. La lumière est douce.
+papa|C'est l'heure.
+narrateur|Bénédicte revient. Elle prend encore la brosse. Papa, l'adulte, se brosse aussi. Matin et soir, c'est pareil. La brosse chatouille un peu.
+papa|Matin et soir, avec un adulte.
+narrateur|Bénédicte répète : matin, soir, brosse. Elle pose la brosse dans le gobelet.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Bénédicte se brosse les dents. Quand et avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Bénédicte a pris la brosse. Elle brosse avec l'adulte. C'est papa. Matin et soir.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Bénédicte met son pyjama. Papa baisse la petite lumière.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.002-05.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Bénédicte répète : matin, soir, brosse. Elle pose la brosse dans le gobelet.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Bénédicte se brosse les dents. Quand et avec quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1683,7 @@
           <t>narrateur|Bénédicte a pris la brosse. Elle brosse avec l'adulte. C'est papa. Matin et soir.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1847,7 @@
           <t>narrateur|Bénédicte met son pyjama. Papa baisse la petite lumière.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.002-05.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bénédicte prend la brosse</t>
+          <t>La brosse jaune de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une bande de soleil sur les carreaux. La brosse jaune attend. Sarah se brosse matin et soir avec papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, le soleil entre dans la salle de bain. Bénédicte sent l'eau tiède. Papa l'appelle. Papa tend la brosse jaune. Bénédicte prend la brosse. Un adulte est avec elle. C'est papa. Ils se brossent ensemble. La brosse va en haut. La brosse va en bas. Bénédicte sent la mousse. Ça goûte un peu la menthe. Parce qu'elle brosse le matin, ses dents sont propres. Elle rince sa bouche. Elle range la brosse. Plus tard, le soir arrive. La lumière est douce. C'est l'heure. Bénédicte revient. Elle prend encore la brosse. Papa, l'adulte, se brosse aussi. Matin et soir, c'est pareil. La brosse chatouille un peu. Matin et soir, avec un adulte. Bénédicte répète : matin, soir, brosse. Elle pose la brosse dans le gobelet.</t>
+          <t>Une bande de soleil coupe les carreaux. Les carreaux sont tièdes, tout lisses. Les chaussons de papa font clap, clap. Une goutte tremble au bout du robinet. Elle tombe. Elle fait toc. La brosse jaune attend dans un gobelet. Sarah, tu as vu le soleil ? Oui, papa. Sur le sol. La goutte a fait toc. Encore une ? On écoute. Une autre goutte tombe. En ce moment, Sarah entre. L'eau tiède coule dans le lavabo. C'est l'heure de la brosse. Papa tend la brosse jaune. Sarah prend la brosse. Un adulte est avec elle. C'est papa, près du miroir. On se brosse ensemble. Moi, l'adulte, je prends la mienne. La brosse va en haut. La brosse va en bas. Ça pique un peu. C'est la menthe. La mousse est blanche et légère. Elle sent bon. Bravo. Tu prends bien la brosse. Le matin, on prend la brosse. Avec un adulte. Avec toi. Oui. Avec moi. Sarah rince sa bouche. L'eau chante dans le lavabo. Elle pose la brosse dans le gobelet. Les dents sont propres, ce matin. Elles brillent ? Oui. Comme le soleil. La bande de soleil a bougé. Elle touche maintenant le tapis. Les chaussons font encore clap, clap. On va au petit déjeuner, après. Après la brosse. Oui. Matin, la brosse, puis le pain. Tu as fini de ranger la brosse ? Oui, papa. Plus tard, le soir arrive. La lumière de la lampe est douce. Les carreaux ne sont plus chauds. C'est le soir, Sarah. C'est l'heure de la brosse. La jaune ? Oui. Matin et soir. Sarah revient près du lavabo. Elle prend encore la brosse jaune. Papa, l'adulte, se brosse aussi. La brosse va en haut. La brosse va en bas. Ça chatouille. Matin et soir, avec un adulte. Matin, soir, brosse. Bravo, Sarah. C'est du bon travail. Sarah rince sa bouche. Elle range la brosse dans le gobelet. Une goutte tremble encore. Tu as fini ? Oui. La brosse est rangée. Les dents brillent, ce soir aussi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,79 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le matin, le soleil entre dans la salle de bain. Bénédicte sent l'eau tiède. Papa l'appelle. Papa tend la brosse jaune. Bénédicte prend la brosse. Un adulte est avec elle. C'est papa. Ils se brossent ensemble. La brosse va en haut. La brosse va en bas. Bénédicte sent la mousse. Ça goûte un peu la menthe. Parce qu'elle brosse le matin, ses dents sont propres. Elle rince sa bouche. Elle range la brosse. Plus tard, le soir arrive. La lumière est douce.
-papa|C'est l'heure.
-narrateur|Bénédicte revient. Elle prend encore la brosse. Papa, l'adulte, se brosse aussi. Matin et soir, c'est pareil. La brosse chatouille un peu.
+          <t>narrateur|Une bande de soleil coupe les carreaux.
+narrateur|Les carreaux sont tièdes, tout lisses.
+narrateur|Les chaussons de papa font clap, clap.
+narrateur|Une goutte tremble au bout du robinet.
+narrateur|Elle tombe. Elle fait toc.
+narrateur|La brosse jaune attend dans un gobelet.
+papa|Sarah, tu as vu le soleil ?
+enfant-f|Oui, papa. Sur le sol.
+papa|La goutte a fait toc.
+enfant-f|Encore une ?
+papa|On écoute.
+narrateur|Une autre goutte tombe.
+narrateur|En ce moment, Sarah entre.
+narrateur|L'eau tiède coule dans le lavabo.
+papa|C'est l'heure de la brosse.
+narrateur|Papa tend la brosse jaune.
+narrateur|Sarah prend la brosse.
+narrateur|Un adulte est avec elle.
+narrateur|C'est papa, près du miroir.
+papa|On se brosse ensemble.
+papa|Moi, l'adulte, je prends la mienne.
+narrateur|La brosse va en haut.
+narrateur|La brosse va en bas.
+enfant-f|Ça pique un peu.
+papa|C'est la menthe.
+narrateur|La mousse est blanche et légère.
+enfant-f|Elle sent bon.
+papa|Bravo. Tu prends bien la brosse.
+papa|Le matin, on prend la brosse.
+papa|Avec un adulte.
+enfant-f|Avec toi.
+papa|Oui. Avec moi.
+narrateur|Sarah rince sa bouche.
+narrateur|L'eau chante dans le lavabo.
+narrateur|Elle pose la brosse dans le gobelet.
+papa|Les dents sont propres, ce matin.
+enfant-f|Elles brillent ?
+papa|Oui. Comme le soleil.
+narrateur|La bande de soleil a bougé.
+narrateur|Elle touche maintenant le tapis.
+narrateur|Les chaussons font encore clap, clap.
+papa|On va au petit déjeuner, après.
+enfant-f|Après la brosse.
+papa|Oui. Matin, la brosse, puis le pain.
+papa|Tu as fini de ranger la brosse ?
+enfant-f|Oui, papa.
+narrateur|Plus tard, le soir arrive.
+narrateur|La lumière de la lampe est douce.
+narrateur|Les carreaux ne sont plus chauds.
+papa|C'est le soir, Sarah.
+papa|C'est l'heure de la brosse.
+enfant-f|La jaune ?
+papa|Oui. Matin et soir.
+narrateur|Sarah revient près du lavabo.
+narrateur|Elle prend encore la brosse jaune.
+narrateur|Papa, l'adulte, se brosse aussi.
+narrateur|La brosse va en haut.
+narrateur|La brosse va en bas.
+enfant-f|Ça chatouille.
 papa|Matin et soir, avec un adulte.
-narrateur|Bénédicte répète : matin, soir, brosse. Elle pose la brosse dans le gobelet.</t>
+enfant-f|Matin, soir, brosse.
+papa|Bravo, Sarah. C'est du bon travail.
+narrateur|Sarah rince sa bouche.
+narrateur|Elle range la brosse dans le gobelet.
+narrateur|Une goutte tremble encore.
+papa|Tu as fini ?
+enfant-f|Oui. La brosse est rangée.
+papa|Les dents brillent, ce soir aussi.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>goutte_robinet</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1423,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Bénédicte se brosse les dents. Quand et avec quoi ?</t>
+          <t>Sarah se brosse les dents. Quand et avec quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,10 +1583,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Bénédicte se brosse les dents. Quand et avec quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah se brosse les dents.
+narrateur|Quand et avec quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1536,7 +1611,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Bénédicte a pris la brosse. Elle brosse avec l'adulte. C'est papa. Matin et soir.</t>
+          <t>Sarah a pris la brosse. Elle brosse avec l'adulte. C'est papa. Matin et soir. Tu as pris la brosse ? Oui. Matin et soir. Avec un adulte. Bravo. C'est du bon travail. La bande de soleil n'est plus là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,10 +1755,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Bénédicte a pris la brosse. Elle brosse avec l'adulte. C'est papa. Matin et soir.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah a pris la brosse.
+narrateur|Elle brosse avec l'adulte.
+narrateur|C'est papa.
+narrateur|Matin et soir.
+papa|Tu as pris la brosse ?
+enfant-f|Oui. Matin et soir.
+papa|Avec un adulte. Bravo.
+papa|C'est du bon travail.
+narrateur|La bande de soleil n'est plus là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,7 +1790,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Bénédicte met son pyjama. Papa baisse la petite lumière.</t>
+          <t>Sarah enfile son pyjama rose. Le tissu sent le linge propre. Je baisse la petite lumière ? Oui, papa. Papa baisse la lampe. Le gobelet garde la brosse jaune. Dors bien, Sarah. Bonne nuit.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,10 +1926,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Bénédicte met son pyjama. Papa baisse la petite lumière.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sarah enfile son pyjama rose.
+narrateur|Le tissu sent le linge propre.
+papa|Je baisse la petite lumière ?
+enfant-f|Oui, papa.
+narrateur|Papa baisse la lampe.
+narrateur|Le gobelet garde la brosse jaune.
+papa|Dors bien, Sarah.
+enfant-f|Bonne nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Matin et soir, la brosse. Avec un adulte. Bravo. Une dernière goutte fait toc. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,10 +2100,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Matin et soir, la brosse.
+papa|Avec un adulte. Bravo.
+narrateur|Une dernière goutte fait toc.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2162,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.002-05.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une bande de soleil coupe les carreaux. Les carreaux sont tièdes, tout lisses. Les chaussons de papa font clap, clap. Une goutte tremble au bout du robinet. Elle tombe. Elle fait toc. La brosse jaune attend dans un gobelet. Sarah, tu as vu le soleil ? Oui, papa. Sur le sol. La goutte a fait toc. Encore une ? On écoute. Une autre goutte tombe. En ce moment, Sarah entre. L'eau tiède coule dans le lavabo. C'est l'heure de la brosse. Papa tend la brosse jaune. Sarah prend la brosse. Un adulte est avec elle. C'est papa, près du miroir. On se brosse ensemble. Moi, l'adulte, je prends la mienne. La brosse va en haut. La brosse va en bas. Ça pique un peu. C'est la menthe. La mousse est blanche et légère. Elle sent bon. Bravo. Tu prends bien la brosse. Le matin, on prend la brosse. Avec un adulte. Avec toi. Oui. Avec moi. Sarah rince sa bouche. L'eau chante dans le lavabo. Elle pose la brosse dans le gobelet. Les dents sont propres, ce matin. Elles brillent ? Oui. Comme le soleil. La bande de soleil a bougé. Elle touche maintenant le tapis. Les chaussons font encore clap, clap. On va au petit déjeuner, après. Après la brosse. Oui. Matin, la brosse, puis le pain. Tu as fini de ranger la brosse ? Oui, papa. Plus tard, le soir arrive. La lumière de la lampe est douce. Les carreaux ne sont plus chauds. C'est le soir, Sarah. C'est l'heure de la brosse. La jaune ? Oui. Matin et soir. Sarah revient près du lavabo. Elle prend encore la brosse jaune. Papa, l'adulte, se brosse aussi. La brosse va en haut. La brosse va en bas. Ça chatouille. Matin et soir, avec un adulte. Matin, soir, brosse. Bravo, Sarah. C'est du bon travail. Sarah rince sa bouche. Elle range la brosse dans le gobelet. Une goutte tremble encore. Tu as fini ? Oui. La brosse est rangée. Les dents brillent, ce soir aussi.</t>
+          <t>Une bande de soleil coupe les carreaux. Les carreaux sont tièdes, tout lisses. Les chaussons de papa font clap, clap. Une goutte tremble au bout du robinet. Elle tombe. Elle fait toc. La brosse jaune attend dans un gobelet. Sarah, tu as vu le soleil ? Oui, papa. Sur le sol. La goutte a fait toc. Encore une ? On écoute. Une autre goutte tombe. En ce moment, Sarah entre. L'eau tiède coule dans le lavabo. C'est l'heure de la brosse. Papa tend la brosse jaune. Sarah prend la brosse. Un adulte est avec elle. C'est papa, près du miroir. On se brosse ensemble. Moi, l'adulte, je prends la mienne. La brosse va en haut. La brosse va en bas. Ça pique un peu. C'est la menthe. La mousse est blanche et légère. Elle sent bon. Bravo. Tu prends bien la brosse. Le matin, on prend la brosse. Avec un adulte. Avec toi. Oui. Avec moi. Sarah rince sa bouche. L'eau chante dans le lavabo. Elle pose la brosse dans le gobelet. Les dents sont propres, ce matin. Elles brillent ? Oui. Comme le soleil. La bande de soleil a bougé. Elle touche maintenant le tapis. Les chaussons font encore clap, clap. On va au petit déjeuner, après. Après la brosse. Oui. Matin, la brosse, puis le pain. Tu as fini de ranger la brosse ? Oui, papa. Plus tard, le soir arrive. La lumière de la lampe est douce. Les carreaux ne sont plus chauds. C'est le soir, Sarah. C'est l'heure de la brosse. La jaune ? Oui. Matin et soir. Sarah revient près du lavabo. Elle prend encore la brosse jaune. Papa, l'adulte, se brosse aussi. La brosse va en haut. La brosse va en bas. Ça chatouille. Matin et soir, avec un adulte. Matin, soir, brosse. Sarah rince sa bouche. Elle range la brosse dans le gobelet. Une goutte tremble encore. Tu as fini ? Oui. La brosse est rangée. Les dents brillent, ce soir aussi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;matin&lt;/emphasis&gt;, le soleil entre dans la salle de bain. Bénédicte sent l'eau tiède. Papa l'appelle. Papa tend la brosse jaune. Bénédicte prend la brosse. Un adulte est avec elle. C'est papa. Ils se brossent ensemble. La brosse va en haut. La brosse va en bas. Bénédicte sent la mousse. Ça goûte un peu la menthe. Parce qu'elle brosse le matin, ses dents sont propres. Elle rince sa bouche. Elle range la brosse. Plus tard, le soir arrive. La lumière est douce. Papa dit : c'est l'heure. Bénédicte revient. Elle prend encore la brosse. Papa, l'adulte, se brosse aussi. Matin et soir, c'est pareil. La brosse chatouille un peu. Papa dit : matin et soir, avec un adulte. Bénédicte répète : matin, soir, brosse. Elle pose la brosse dans le gobelet.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une bande de soleil coupe les carreaux. Les carreaux sont tièdes, tout lisses. Les chaussons de papa font clap, clap. Une goutte tremble au bout du robinet. Elle tombe. Elle fait toc. La brosse jaune attend dans un gobelet. Sarah, tu as vu le soleil ? Oui, papa. Sur le sol. La goutte a fait toc. Encore une ? On écoute. Une autre goutte tombe. En ce moment, Sarah entre. L'eau tiède coule dans le lavabo. C'est l'heure de la brosse. Papa tend la brosse jaune. Sarah prend la brosse. Un adulte est avec elle. C'est papa, près du miroir. On se brosse ensemble. Moi, l'adulte, je prends la mienne. La brosse va en haut. La brosse va en bas. Ça pique un peu. C'est la menthe. La mousse est blanche et légère. Elle sent bon. Bravo. Tu prends bien la brosse. Le matin, on prend la brosse. Avec un adulte. Avec toi. Oui. Avec moi. Sarah rince sa bouche. L'eau chante dans le lavabo. Elle pose la brosse dans le gobelet. Les dents sont propres, ce matin. Elles brillent ? Oui. Comme le soleil. La bande de soleil a bougé. Elle touche maintenant le tapis. Les chaussons font encore clap, clap. On va au petit déjeuner, après. Après la brosse. Oui. Matin, la brosse, puis le pain. Tu as fini de ranger la brosse ? Oui, papa. Plus tard, le soir arrive. La lumière de la lampe est douce. Les carreaux ne sont plus chauds. C'est le soir, Sarah. C'est l'heure de la brosse. La jaune ? Oui. Matin et soir. Sarah revient près du lavabo. Elle prend encore la brosse jaune. Papa, l'adulte, se brosse aussi. La brosse va en haut. La brosse va en bas. Ça chatouille. Matin et soir, avec un adulte. Matin, soir, brosse. Sarah rince sa bouche. Elle range la brosse dans le gobelet. Une goutte tremble encore. Tu as fini ? Oui. La brosse est rangée. Les dents brillent, ce soir aussi.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1385,7 +1385,6 @@
 enfant-f|Ça chatouille.
 papa|Matin et soir, avec un adulte.
 enfant-f|Matin, soir, brosse.
-papa|Bravo, Sarah. C'est du bon travail.
 narrateur|Sarah rince sa bouche.
 narrateur|Elle range la brosse dans le gobelet.
 narrateur|Une goutte tremble encore.
@@ -1428,7 +1427,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Bénédicte se &lt;emphasis level="moderate"&gt;brosse&lt;/emphasis&gt; les dents. Quand et avec quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah se brosse les dents. Quand et avec quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1611,12 +1610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a pris la brosse. Elle brosse avec l'adulte. C'est papa. Matin et soir. Tu as pris la brosse ? Oui. Matin et soir. Avec un adulte. Bravo. C'est du bon travail. La bande de soleil n'est plus là.</t>
+          <t>Sarah a pris la brosse. Elle brosse avec l'adulte. C'est papa. Matin et soir. Tu as pris la brosse ? Oui. Matin et soir. Avec un adulte. Bravo. La bande de soleil n'est plus là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bénédicte a pris la brosse. Elle brosse avec l'adulte. C'est papa. &lt;emphasis level="moderate"&gt;matin&lt;/emphasis&gt; et soir.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a pris la brosse. Elle brosse avec l'adulte. C'est papa. Matin et soir. Tu as pris la brosse ? Oui. Matin et soir. Avec un adulte. Bravo. La bande de soleil n'est plus là.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1762,7 +1761,6 @@
 papa|Tu as pris la brosse ?
 enfant-f|Oui. Matin et soir.
 papa|Avec un adulte. Bravo.
-papa|C'est du bon travail.
 narrateur|La bande de soleil n'est plus là.</t>
         </is>
       </c>
@@ -1795,7 +1793,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bénédicte met son pyjama. Papa baisse la petite lumière.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah enfile son pyjama rose. Le tissu sent le linge propre. Je baisse la petite lumière ? Oui, papa. Papa baisse la lampe. Le gobelet garde la brosse jaune. Dors bien, Sarah. Bonne nuit.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1960,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Matin et soir, la brosse. Avec un adulte. Bravo. Une dernière goutte fait toc. L'histoire est finie.</t>
+          <t>Matin et soir, la brosse. Avec un adulte. Bravo. Une dernière goutte fait toc.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Matin et soir, la brosse. Avec un adulte. Bravo. Une dernière goutte fait toc.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2102,8 +2100,7 @@
         <is>
           <t>enfant-f|Matin et soir, la brosse.
 papa|Avec un adulte. Bravo.
-narrateur|Une dernière goutte fait toc.
-narrateur|L'histoire est finie.</t>
+narrateur|Une dernière goutte fait toc.</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2169,6 +2166,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.002-05.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salle de bain</t>
+          <t>salle de bain, bande de soleil, goutte au robinet</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bénédicte, papa</t>
+          <t>Sarah, papa</t>
         </is>
       </c>
     </row>
